--- a/listing-monitor/reports/2026-10-17/qa_2026-10-17.xlsx
+++ b/listing-monitor/reports/2026-10-17/qa_2026-10-17.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cần xác nhận" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CFS'!$A$1:$N$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CFS'!$A$1:$N$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tạo lúc 2026-10-17 22:26. Mức độ: Cao = sai thông tin / gây confuse khách và Google; Trung bình = cần sửa; Thấp = nên sửa.</t>
+          <t>Tạo lúc 2026-10-18 17:58. Mức độ: Cao = sai thông tin / gây confuse khách và Google; Trung bình = cần sửa; Thấp = nên sửa.</t>
         </is>
       </c>
     </row>
@@ -538,13 +538,13 @@
         <v>35</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>112</v>
@@ -594,153 +594,179 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>Sai team</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Category / Tag</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Words to Avoid</t>
+          <t>Category / Tag</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Sai đối tượng</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Words to Avoid</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>35</v>
+      </c>
+      <c r="C15" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B16" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C16" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Lỗi lặp lại trên phần lớn listing của 1 site (nhiều khả năng do TEMPLATE, sửa template 1 lần)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Nhóm</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Vị trí</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Lỗi</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Số listing</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>CFS</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>SEO</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Meta description</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>khoảng trắng trước dấu câu</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>35/35</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>CFS</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Ảnh</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Số lượng ảnh</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Chỉ có 2 ảnh sản phẩm</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>22/35</t>
         </is>
@@ -757,7 +783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N121"/>
+  <dimension ref="A1:N124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1023,32 +1049,32 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Trung bình</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Cao</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 02:28</t>
+          <t>2026-10-17 08:05</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83990</v>
+        <v>84258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CFS_ARG_GK_ADK_No_2026</t>
+          <t>CFS_USA_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Argentina World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
+          <t>USA World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Words to Avoid</t>
+          <t>Sai team</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1058,18 +1084,18 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>'badge' (...3 letters and 2 digits. Chest badge: World Cup 2022 Champions can...)</t>
+          <t>Kit Facts trong description ghi Team: Uruguay, nhưng listing là USA</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>badge -&gt; chest detail</t>
+          <t>Viết lại description cho đúng team (đang copy từ listing khác)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -1088,20 +1114,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-17 02:41</t>
+          <t>2026-10-17 02:28</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>83998</v>
+        <v>83990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CFS_ARG_GK_ADK_E.MARTINEZ 23_2026</t>
+          <t>CFS_ARG_GK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit</t>
+          <t>Argentina World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1116,7 +1142,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>'badge' (... and cannot be changed. Chest badge: World Cup 2022 Champions can...)</t>
+          <t>'badge' (...3 letters and 2 digits. Chest badge: World Cup 2022 Champions can...)</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1127,7 +1153,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-e-martinez-23-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -1146,46 +1172,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-17 07:58</t>
+          <t>2026-10-17 02:41</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84250</v>
+        <v>83998</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CFS_URU_AW_ADK_No_2026</t>
+          <t>CFS_ARG_GK_ADK_E.MARTINEZ 23_2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Uruguay World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Category / Tag</t>
+          <t>Words to Avoid</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Category 'South Africa' không liên quan tới tên sản phẩm (copy từ listing khác?)</t>
+          <t>'badge' (... and cannot be changed. Chest badge: World Cup 2022 Champions can...)</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Xoá/sửa category</t>
+          <t>badge -&gt; chest detail</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/uruguay-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-e-martinez-23-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -1204,46 +1230,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-17 08:05</t>
+          <t>2026-10-17 03:12</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>84258</v>
+        <v>84031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CFS_USA_AW_ADK_No_2026</t>
+          <t>CFS_CHE_BlueTN_ADK_No_2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USA World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>Chelsea Blue Training Adult Cheap Football Kit 2026/27</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Category / Tag</t>
+          <t>Sai đối tượng</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Ảnh (alt/tên file)</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Category 'South Africa' không liên quan tới tên sản phẩm (copy từ listing khác?)</t>
+          <t>Listing Men/Adult nhưng ảnh ghi: "Chelsea Blue Training Kids Football Kit 2026 27 Front View"</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Xoá/sửa category</t>
+          <t>Kiểm tra có upload nhầm bộ ảnh của đối tượng khác không</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/chelsea-blue-training-adult-cheap-football-kit-2026-27/</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -1262,46 +1288,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-17 08:12</t>
+          <t>2026-10-17 04:16</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>84266</v>
+        <v>84116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CFS_USA_HO_ADK_No_2026</t>
+          <t>CFS_ENG_HO_ADK_RICE 4_2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USA World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 RICE 4 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Category / Tag</t>
+          <t>Sai đối tượng</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Ảnh (alt/tên file)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Category 'South Africa' không liên quan tới tên sản phẩm (copy từ listing khác?)</t>
+          <t>Listing Men/Adult nhưng ảnh ghi: "England World Cup 2026 Home Kids Cheap Football Kit – RICE 4"</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Xoá/sửa category</t>
+          <t>Kiểm tra có upload nhầm bộ ảnh của đối tượng khác không</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -1313,53 +1339,53 @@
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Thấp</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-17 02:28</t>
+          <t>2026-10-17 07:58</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83990</v>
+        <v>84250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CFS_ARG_GK_ADK_No_2026</t>
+          <t>CFS_URU_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Argentina World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
+          <t>Uruguay World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Category / Tag</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 175 ký tự (nên &lt;= 160)</t>
+          <t>Category 'South Africa' không liên quan tới tên sản phẩm (copy từ listing khác?)</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Xoá/sửa category</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/uruguay-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1371,53 +1397,53 @@
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Thấp</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-17 02:41</t>
+          <t>2026-10-17 08:05</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83998</v>
+        <v>84258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CFS_ARG_GK_ADK_E.MARTINEZ 23_2026</t>
+          <t>CFS_USA_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit</t>
+          <t>USA World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Category / Tag</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SEO title</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>SEO title dài 74 ký tự (nên &lt;= 60)</t>
+          <t>Category 'South Africa' không liên quan tới tên sản phẩm (copy từ listing khác?)</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Xoá/sửa category</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-e-martinez-23-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1429,53 +1455,53 @@
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Thấp</t>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-17 02:41</t>
+          <t>2026-10-17 08:12</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83998</v>
+        <v>84266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CFS_ARG_GK_ADK_E.MARTINEZ 23_2026</t>
+          <t>CFS_USA_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit</t>
+          <t>USA World Cup 2026 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Category / Tag</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 189 ký tự (nên &lt;= 160)</t>
+          <t>Category 'South Africa' không liên quan tới tên sản phẩm (copy từ listing khác?)</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Xoá/sửa category</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-e-martinez-23-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -1494,46 +1520,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-17 02:41</t>
+          <t>2026-10-17 02:28</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>83998</v>
+        <v>83990</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CFS_ARG_GK_ADK_E.MARTINEZ 23_2026</t>
+          <t>CFS_ARG_GK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit</t>
+          <t>Argentina World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SKU (Google)</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_ARG_GK_ADK_E.MARTINEZ 23_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>Meta dài 175 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-e-martinez-23-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -1552,20 +1578,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-17 02:49</t>
+          <t>2026-10-17 02:41</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>84006</v>
+        <v>83998</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_No_2026</t>
+          <t>CFS_ARG_GK_ADK_E.MARTINEZ 23_2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>England World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1575,12 +1601,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SEO title</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 167 ký tự (nên &lt;= 160)</t>
+          <t>SEO title dài 74 ký tự (nên &lt;= 60)</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1591,7 +1617,7 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-e-martinez-23-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -1610,20 +1636,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-17 03:06</t>
+          <t>2026-10-17 02:41</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>84023</v>
+        <v>83998</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CFS_CHE_BlackTN_ADK_No_2026</t>
+          <t>CFS_ARG_GK_ADK_E.MARTINEZ 23_2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chelsea Black Training Adult Cheap Football Kit 2026/27</t>
+          <t>Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1638,7 +1664,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 170 ký tự (nên &lt;= 160)</t>
+          <t>Meta dài 189 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -1649,7 +1675,7 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/chelsea-black-training-adult-cheap-football-kit-2026-27/</t>
+          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-e-martinez-23-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -1668,46 +1694,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-17 03:12</t>
+          <t>2026-10-17 02:41</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>84031</v>
+        <v>83998</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CFS_CHE_BlueTN_ADK_No_2026</t>
+          <t>CFS_ARG_GK_ADK_E.MARTINEZ 23_2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelsea Blue Training Adult Cheap Football Kit 2026/27</t>
+          <t>Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SKU (Google)</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 169 ký tự (nên &lt;= 160)</t>
+          <t>SKU 'CFS_ARG_GK_ADK_E.MARTINEZ 23_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/chelsea-blue-training-adult-cheap-football-kit-2026-27/</t>
+          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-e-martinez-23-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -1726,20 +1752,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-17 03:18</t>
+          <t>2026-10-17 02:49</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>84039</v>
+        <v>84006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_No_2026</t>
+          <t>CFS_ENG_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>England World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1765,7 +1791,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -1784,20 +1810,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-17 03:24</t>
+          <t>2026-10-17 03:06</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>84047</v>
+        <v>84023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_BELLINGHAM 10_2026</t>
+          <t>CFS_CHE_BlackTN_ADK_No_2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>England World Cup 2026 BELLINGHAM 10 Away Adult Cheap Football Kit</t>
+          <t>Chelsea Black Training Adult Cheap Football Kit 2026/27</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1807,12 +1833,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SEO title</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>SEO title dài 66 ký tự (nên &lt;= 60)</t>
+          <t>Meta dài 170 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1823,7 +1849,7 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/chelsea-black-training-adult-cheap-football-kit-2026-27/</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -1842,20 +1868,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-17 03:24</t>
+          <t>2026-10-17 03:12</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>84047</v>
+        <v>84031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_BELLINGHAM 10_2026</t>
+          <t>CFS_CHE_BlueTN_ADK_No_2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>England World Cup 2026 BELLINGHAM 10 Away Adult Cheap Football Kit</t>
+          <t>Chelsea Blue Training Adult Cheap Football Kit 2026/27</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1870,7 +1896,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 181 ký tự (nên &lt;= 160)</t>
+          <t>Meta dài 169 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1881,7 +1907,7 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/chelsea-blue-training-adult-cheap-football-kit-2026-27/</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -1900,46 +1926,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-17 03:24</t>
+          <t>2026-10-17 03:18</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>84047</v>
+        <v>84039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_BELLINGHAM 10_2026</t>
+          <t>CFS_ENG_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>England World Cup 2026 BELLINGHAM 10 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SKU (Google)</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_ENG_AW_ADK_BELLINGHAM 10_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>Meta dài 167 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -1958,20 +1984,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-17 03:31</t>
+          <t>2026-10-17 03:24</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>84055</v>
+        <v>84047</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_KANE 9_2026</t>
+          <t>CFS_ENG_AW_ADK_BELLINGHAM 10_2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>England World Cup 2026 KANE 9 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 BELLINGHAM 10 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1981,12 +2007,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SEO title</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 174 ký tự (nên &lt;= 160)</t>
+          <t>SEO title dài 66 ký tự (nên &lt;= 60)</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -1997,7 +2023,7 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2016,46 +2042,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-17 03:31</t>
+          <t>2026-10-17 03:24</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>84055</v>
+        <v>84047</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_KANE 9_2026</t>
+          <t>CFS_ENG_AW_ADK_BELLINGHAM 10_2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>England World Cup 2026 KANE 9 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 BELLINGHAM 10 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SKU (Google)</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_ENG_AW_ADK_KANE 9_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>Meta dài 181 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -2074,46 +2100,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-17 03:36</t>
+          <t>2026-10-17 03:24</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>84063</v>
+        <v>84047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_RICE 4_2026</t>
+          <t>CFS_ENG_AW_ADK_BELLINGHAM 10_2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>England World Cup 2026 RICE 4 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 BELLINGHAM 10 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SKU (Google)</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 174 ký tự (nên &lt;= 160)</t>
+          <t>SKU 'CFS_ENG_AW_ADK_BELLINGHAM 10_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -2132,46 +2158,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-17 03:36</t>
+          <t>2026-10-17 03:31</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>84063</v>
+        <v>84055</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_RICE 4_2026</t>
+          <t>CFS_ENG_AW_ADK_KANE 9_2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>England World Cup 2026 RICE 4 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 KANE 9 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SKU (Google)</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_ENG_AW_ADK_RICE 4_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>Meta dài 174 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -2190,46 +2216,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-17 03:40</t>
+          <t>2026-10-17 03:31</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>84071</v>
+        <v>84055</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_SAKA 7_2026</t>
+          <t>CFS_ENG_AW_ADK_KANE 9_2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>England World Cup 2026 SAKA 7 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 KANE 9 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SKU (Google)</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 174 ký tự (nên &lt;= 160)</t>
+          <t>SKU 'CFS_ENG_AW_ADK_KANE 9_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -2248,46 +2274,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-17 03:40</t>
+          <t>2026-10-17 03:36</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>84071</v>
+        <v>84063</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_SAKA 7_2026</t>
+          <t>CFS_ENG_AW_ADK_RICE 4_2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>England World Cup 2026 SAKA 7 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 RICE 4 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SKU (Google)</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_ENG_AW_ADK_SAKA 7_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>Meta dài 174 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -2306,46 +2332,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-17 03:47</t>
+          <t>2026-10-17 03:36</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>84079</v>
+        <v>84063</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CFS_ENG_BlueGK_ADK_No_2026</t>
+          <t>CFS_ENG_AW_ADK_RICE 4_2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>England World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 RICE 4 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SKU (Google)</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 178 ký tự (nên &lt;= 160)</t>
+          <t>SKU 'CFS_ENG_AW_ADK_RICE 4_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-blue-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
@@ -2364,20 +2390,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-17 03:58</t>
+          <t>2026-10-17 03:40</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>84089</v>
+        <v>84071</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CFS_ENG_YellowGK_ADK_No_2026</t>
+          <t>CFS_ENG_AW_ADK_SAKA 7_2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>England World Cup 2026 Yellow Goalkeeper Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 SAKA 7 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2392,7 +2418,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 180 ký tự (nên &lt;= 160)</t>
+          <t>Meta dài 174 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2403,7 +2429,7 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-yellow-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -2422,46 +2448,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-17 04:06</t>
+          <t>2026-10-17 03:40</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>84098</v>
+        <v>84071</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_BELLINGHAM 10_2026</t>
+          <t>CFS_ENG_AW_ADK_SAKA 7_2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>England World Cup 2026 BELLINGHAM 10 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 SAKA 7 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SEO title</t>
+          <t>SKU (Google)</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>SEO title dài 66 ký tự (nên &lt;= 60)</t>
+          <t>SKU 'CFS_ENG_AW_ADK_SAKA 7_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
@@ -2480,20 +2506,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-17 04:06</t>
+          <t>2026-10-17 03:47</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>84098</v>
+        <v>84079</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_BELLINGHAM 10_2026</t>
+          <t>CFS_ENG_BlueGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>England World Cup 2026 BELLINGHAM 10 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2508,7 +2534,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 181 ký tự (nên &lt;= 160)</t>
+          <t>Meta dài 178 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2519,7 +2545,7 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-blue-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
@@ -2538,46 +2564,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-17 04:06</t>
+          <t>2026-10-17 03:58</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>84098</v>
+        <v>84089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_BELLINGHAM 10_2026</t>
+          <t>CFS_ENG_YellowGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>England World Cup 2026 BELLINGHAM 10 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 Yellow Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SKU (Google)</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_ENG_HO_ADK_BELLINGHAM 10_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>Meta dài 180 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-yellow-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
@@ -2596,20 +2622,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-17 04:12</t>
+          <t>2026-10-17 04:06</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>84107</v>
+        <v>84098</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_KANE 9_2026</t>
+          <t>CFS_ENG_HO_ADK_BELLINGHAM 10_2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>England World Cup 2026 KANE 9 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 BELLINGHAM 10 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2619,12 +2645,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SEO title</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 174 ký tự (nên &lt;= 160)</t>
+          <t>SEO title dài 66 ký tự (nên &lt;= 60)</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -2635,7 +2661,7 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
@@ -2654,46 +2680,46 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-17 04:12</t>
+          <t>2026-10-17 04:06</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>84107</v>
+        <v>84098</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_KANE 9_2026</t>
+          <t>CFS_ENG_HO_ADK_BELLINGHAM 10_2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>England World Cup 2026 KANE 9 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 BELLINGHAM 10 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SKU (Google)</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_ENG_HO_ADK_KANE 9_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>Meta dài 181 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
@@ -2712,46 +2738,46 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-17 04:16</t>
+          <t>2026-10-17 04:06</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>84116</v>
+        <v>84098</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_RICE 4_2026</t>
+          <t>CFS_ENG_HO_ADK_BELLINGHAM 10_2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>England World Cup 2026 RICE 4 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 BELLINGHAM 10 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SKU (Google)</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 174 ký tự (nên &lt;= 160)</t>
+          <t>SKU 'CFS_ENG_HO_ADK_BELLINGHAM 10_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
@@ -2770,46 +2796,46 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-17 04:16</t>
+          <t>2026-10-17 04:12</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>84116</v>
+        <v>84107</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_RICE 4_2026</t>
+          <t>CFS_ENG_HO_ADK_KANE 9_2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>England World Cup 2026 RICE 4 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 KANE 9 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SKU (Google)</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_ENG_HO_ADK_RICE 4_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>Meta dài 174 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
@@ -2828,46 +2854,46 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-17 04:20</t>
+          <t>2026-10-17 04:12</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>84125</v>
+        <v>84107</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_SAKA 7_2026</t>
+          <t>CFS_ENG_HO_ADK_KANE 9_2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>England World Cup 2026 SAKA 7 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 KANE 9 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SKU (Google)</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 174 ký tự (nên &lt;= 160)</t>
+          <t>SKU 'CFS_ENG_HO_ADK_KANE 9_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
@@ -2886,46 +2912,46 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-17 04:20</t>
+          <t>2026-10-17 04:16</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>84125</v>
+        <v>84116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_SAKA 7_2026</t>
+          <t>CFS_ENG_HO_ADK_RICE 4_2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>England World Cup 2026 SAKA 7 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 RICE 4 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SKU (Google)</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_ENG_HO_ADK_SAKA 7_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>Meta dài 174 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
@@ -2944,46 +2970,46 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-17 06:47</t>
+          <t>2026-10-17 04:16</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>84135</v>
+        <v>84116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CFS_GER_AWGK_ADK_No_2026</t>
+          <t>CFS_ENG_HO_ADK_RICE 4_2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Germany World Cup 2026 Away Goalkeeper Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 RICE 4 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SKU (Google)</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 178 ký tự (nên &lt;= 160)</t>
+          <t>SKU 'CFS_ENG_HO_ADK_RICE 4_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/germany-world-cup-2026-away-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
@@ -3002,46 +3028,46 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-17 06:54</t>
+          <t>2026-10-17 04:20</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>84143</v>
+        <v>84125</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CFS_JP_HO_ADK_No_2026</t>
+          <t>CFS_ENG_HO_ADK_SAKA 7_2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Japan World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 SAKA 7 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alt text</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Alt text bị trùng giữa các ảnh: "Japan World Cup 2026 Home Adult Cheap Football Kit - Front View"</t>
+          <t>Meta dài 174 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Mỗi ảnh 1 alt riêng</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/japan-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
@@ -3060,46 +3086,46 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-17 06:54</t>
+          <t>2026-10-17 04:20</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>84143</v>
+        <v>84125</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CFS_JP_HO_ADK_No_2026</t>
+          <t>CFS_ENG_HO_ADK_SAKA 7_2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Japan World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 SAKA 7 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>SKU (Google)</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 1 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>SKU 'CFS_ENG_HO_ADK_SAKA 7_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/japan-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
@@ -3118,20 +3144,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-17 06:59</t>
+          <t>2026-10-17 06:47</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>84151</v>
+        <v>84135</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CFS_NTL_BlackGK_ADK_No_2026</t>
+          <t>CFS_GER_AWGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Netherlands World Cup 2026 Black Goalkeeper Adult Cheap Football Kit</t>
+          <t>Germany World Cup 2026 Away Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3141,12 +3167,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SEO title</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>SEO title dài 68 ký tự (nên &lt;= 60)</t>
+          <t>Meta dài 178 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -3157,7 +3183,7 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-black-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/germany-world-cup-2026-away-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
@@ -3176,46 +3202,46 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-17 06:59</t>
+          <t>2026-10-17 06:54</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>84151</v>
+        <v>84143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CFS_NTL_BlackGK_ADK_No_2026</t>
+          <t>CFS_JP_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Netherlands World Cup 2026 Black Goalkeeper Adult Cheap Football Kit</t>
+          <t>Japan World Cup 2026 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Alt text</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 183 ký tự (nên &lt;= 160)</t>
+          <t>Alt text bị trùng giữa các ảnh: "Japan World Cup 2026 Home Adult Cheap Football Kit - Front View"</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Mỗi ảnh 1 alt riêng</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-black-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/japan-world-cup-2026-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -3234,46 +3260,46 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-17 07:05</t>
+          <t>2026-10-17 06:54</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>84159</v>
+        <v>84143</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CFS_NTL_GreenGK_ADK_No_2026</t>
+          <t>CFS_JP_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Netherlands World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
+          <t>Japan World Cup 2026 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SEO title</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>SEO title dài 68 ký tự (nên &lt;= 60)</t>
+          <t>Chỉ có 1 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/japan-world-cup-2026-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -3292,20 +3318,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-17 07:05</t>
+          <t>2026-10-17 06:59</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>84159</v>
+        <v>84151</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CFS_NTL_GreenGK_ADK_No_2026</t>
+          <t>CFS_NTL_BlackGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Netherlands World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
+          <t>Netherlands World Cup 2026 Black Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3315,12 +3341,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SEO title</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 183 ký tự (nên &lt;= 160)</t>
+          <t>SEO title dài 68 ký tự (nên &lt;= 60)</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -3331,7 +3357,7 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-black-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
@@ -3350,20 +3376,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-17 07:09</t>
+          <t>2026-10-17 06:59</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>84167</v>
+        <v>84151</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CFS_SCL_AW_ADK_No_2026</t>
+          <t>CFS_NTL_BlackGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>Netherlands World Cup 2026 Black Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3378,7 +3404,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 168 ký tự (nên &lt;= 160)</t>
+          <t>Meta dài 183 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -3389,7 +3415,7 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-black-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
@@ -3408,20 +3434,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-17 07:14</t>
+          <t>2026-10-17 07:05</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>84176</v>
+        <v>84159</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CFS_SCL_AW_ADK_McTOMINAY 4_2026</t>
+          <t>CFS_NTL_GreenGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 McTOMINAY 4 Away Adult Cheap Football Kit</t>
+          <t>Netherlands World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3431,12 +3457,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SEO title</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 180 ký tự (nên &lt;= 160)</t>
+          <t>SEO title dài 68 ký tự (nên &lt;= 60)</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -3447,7 +3473,7 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
@@ -3466,46 +3492,46 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-17 07:14</t>
+          <t>2026-10-17 07:05</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>84176</v>
+        <v>84159</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CFS_SCL_AW_ADK_McTOMINAY 4_2026</t>
+          <t>CFS_NTL_GreenGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 McTOMINAY 4 Away Adult Cheap Football Kit</t>
+          <t>Netherlands World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SKU (Google)</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_SCL_AW_ADK_McTOMINAY 4_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>Meta dài 183 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
@@ -3524,20 +3550,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-17 07:23</t>
+          <t>2026-10-17 07:09</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>84185</v>
+        <v>84167</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CFS_SCL_HO_ADK_No_2026</t>
+          <t>CFS_SCL_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3563,7 +3589,7 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
@@ -3582,20 +3608,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-17 07:27</t>
+          <t>2026-10-17 07:14</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>84193</v>
+        <v>84176</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CFS_SCL_HO_ADK_McTOMINAY 4_2026</t>
+          <t>CFS_SCL_AW_ADK_McTOMINAY 4_2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 McTOMINAY 4 Home Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 McTOMINAY 4 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3621,7 +3647,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
@@ -3640,20 +3666,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-17 07:27</t>
+          <t>2026-10-17 07:14</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>84193</v>
+        <v>84176</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CFS_SCL_HO_ADK_McTOMINAY 4_2026</t>
+          <t>CFS_SCL_AW_ADK_McTOMINAY 4_2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 McTOMINAY 4 Home Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 McTOMINAY 4 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3668,7 +3694,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_SCL_HO_ADK_McTOMINAY 4_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>SKU 'CFS_SCL_AW_ADK_McTOMINAY 4_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -3679,7 +3705,7 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
@@ -3698,20 +3724,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-17 07:32</t>
+          <t>2026-10-17 07:23</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>84203</v>
+        <v>84185</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CFS_SCL_HO_ADK_MCGINN 7_2026</t>
+          <t>CFS_SCL_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 MCGINN 7 Home Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3726,7 +3752,7 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 177 ký tự (nên &lt;= 160)</t>
+          <t>Meta dài 168 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -3737,7 +3763,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mcginn-7-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
@@ -3756,46 +3782,46 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-17 07:32</t>
+          <t>2026-10-17 07:27</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>84203</v>
+        <v>84193</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CFS_SCL_HO_ADK_MCGINN 7_2026</t>
+          <t>CFS_SCL_HO_ADK_McTOMINAY 4_2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 MCGINN 7 Home Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 McTOMINAY 4 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SKU (Google)</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_SCL_HO_ADK_MCGINN 7_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>Meta dài 180 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mcginn-7-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
@@ -3814,46 +3840,46 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-17 07:36</t>
+          <t>2026-10-17 07:27</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>84212</v>
+        <v>84193</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CFS_SPA_BlueGK_ADK_No_2026</t>
+          <t>CFS_SCL_HO_ADK_McTOMINAY 4_2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 McTOMINAY 4 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SKU (Google)</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 176 ký tự (nên &lt;= 160)</t>
+          <t>SKU 'CFS_SCL_HO_ADK_McTOMINAY 4_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-blue-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
@@ -3872,46 +3898,46 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-17 07:36</t>
+          <t>2026-10-17 07:32</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>84212</v>
+        <v>84203</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CFS_SPA_BlueGK_ADK_No_2026</t>
+          <t>CFS_SCL_HO_ADK_MCGINN 7_2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 MCGINN 7 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 1 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>Meta dài 177 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-blue-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mcginn-7-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
@@ -3930,46 +3956,46 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-17 07:41</t>
+          <t>2026-10-17 07:32</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>84219</v>
+        <v>84203</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CFS_SPA_GK_ADK_No_2026</t>
+          <t>CFS_SCL_HO_ADK_MCGINN 7_2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 MCGINN 7 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SKU (Google)</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 171 ký tự (nên &lt;= 160)</t>
+          <t>SKU 'CFS_SCL_HO_ADK_MCGINN 7_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mcginn-7-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
@@ -3988,46 +4014,46 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-17 07:41</t>
+          <t>2026-10-17 07:36</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>84219</v>
+        <v>84212</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CFS_SPA_GK_ADK_No_2026</t>
+          <t>CFS_SPA_BlueGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 1 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>Meta dài 176 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-blue-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
@@ -4046,46 +4072,46 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-17 07:44</t>
+          <t>2026-10-17 07:36</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>84226</v>
+        <v>84212</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CFS_SPA_GK_ADK_RAYA 1_2026</t>
+          <t>CFS_SPA_BlueGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 RAYA 1 Goalkeeper Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 178 ký tự (nên &lt;= 160)</t>
+          <t>Chỉ có 1 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-raya-1-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-blue-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
@@ -4104,46 +4130,46 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-17 07:44</t>
+          <t>2026-10-17 07:41</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>84226</v>
+        <v>84219</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CFS_SPA_GK_ADK_RAYA 1_2026</t>
+          <t>CFS_SPA_GK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 RAYA 1 Goalkeeper Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SKU (Google)</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>SKU 'CFS_SPA_GK_ADK_RAYA 1_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
+          <t>Meta dài 171 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-raya-1-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
@@ -4162,46 +4188,46 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-17 07:50</t>
+          <t>2026-10-17 07:41</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>84234</v>
+        <v>84219</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CFS_SPA_GreenGK_ADK_No_2026</t>
+          <t>CFS_SPA_GK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 177 ký tự (nên &lt;= 160)</t>
+          <t>Chỉ có 1 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
@@ -4220,20 +4246,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-17 07:54</t>
+          <t>2026-10-17 07:44</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>84242</v>
+        <v>84226</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CFS_SPA_RedGK_ADK_No_2026</t>
+          <t>CFS_SPA_GK_ADK_RAYA 1_2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 Red Goalkeeper Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 RAYA 1 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4248,7 +4274,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 175 ký tự (nên &lt;= 160)</t>
+          <t>Meta dài 178 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -4259,7 +4285,7 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-red-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-raya-1-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
@@ -4278,46 +4304,46 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-17 07:58</t>
+          <t>2026-10-17 07:44</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>84250</v>
+        <v>84226</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CFS_URU_AW_ADK_No_2026</t>
+          <t>CFS_SPA_GK_ADK_RAYA 1_2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Uruguay World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 RAYA 1 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>SKU (Google)</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Meta dài 167 ký tự (nên &lt;= 160)</t>
+          <t>SKU 'CFS_SPA_GK_ADK_RAYA 1_2026' có dấu cách hoặc ký tự đặc biệt: Google Merchant không nhận</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Rút gọn</t>
+          <t>Dùng chữ không dấu, số, - hoặc _ (vd FERRAN-9)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/uruguay-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-raya-1-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
@@ -4336,46 +4362,46 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-17 08:05</t>
+          <t>2026-10-17 07:50</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>84258</v>
+        <v>84234</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CFS_USA_AW_ADK_No_2026</t>
+          <t>CFS_SPA_GreenGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>USA World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 1 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>Meta dài 177 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
@@ -4394,46 +4420,46 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-17 08:12</t>
+          <t>2026-10-17 07:54</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>84266</v>
+        <v>84242</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CFS_USA_HO_ADK_No_2026</t>
+          <t>CFS_SPA_RedGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>USA World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 Red Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 1 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>Meta dài 175 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-red-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
@@ -4452,46 +4478,46 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-17 08:18</t>
+          <t>2026-10-17 07:58</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>84273</v>
+        <v>84250</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CFS_WAL_HO_ADK_No_2026</t>
+          <t>CFS_URU_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wales World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>Uruguay World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 1 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>Meta dài 167 ký tự (nên &lt;= 160)</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Rút gọn</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/wales-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/uruguay-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
@@ -4510,50 +4536,46 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-17 02:28</t>
+          <t>2026-10-17 08:05</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>83990</v>
+        <v>84258</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CFS_ARG_GK_ADK_No_2026</t>
+          <t>CFS_USA_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Argentina World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
+          <t>USA World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Argentina World Cup 2026 Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 1 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+          <t>Thêm ảnh</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
@@ -4572,20 +4594,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-17 02:28</t>
+          <t>2026-10-17 08:12</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>83990</v>
+        <v>84266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CFS_ARG_GK_ADK_No_2026</t>
+          <t>CFS_USA_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Argentina World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
+          <t>USA World Cup 2026 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4600,7 +4622,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>Chỉ có 1 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -4608,14 +4630,10 @@
           <t>Thêm ảnh</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
@@ -4634,50 +4652,46 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-17 02:41</t>
+          <t>2026-10-17 08:18</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>83998</v>
+        <v>84273</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CFS_ARG_GK_ADK_E.MARTINEZ 23_2026</t>
+          <t>CFS_WAL_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit</t>
+          <t>Wales World Cup 2026 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 1 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+          <t>Thêm ảnh</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-e-martinez-23-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/wales-world-cup-2026-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
@@ -4696,40 +4710,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-17 02:41</t>
+          <t>2026-10-17 02:28</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>83998</v>
+        <v>83990</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CFS_ARG_GK_ADK_E.MARTINEZ 23_2026</t>
+          <t>CFS_ARG_GK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit</t>
+          <t>Argentina World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Argentina World Cup 2026 Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4739,7 +4753,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-e-martinez-23-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
@@ -4758,40 +4772,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-17 02:49</t>
+          <t>2026-10-17 02:28</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>84006</v>
+        <v>83990</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_No_2026</t>
+          <t>CFS_ARG_GK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>England World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>Argentina World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4801,7 +4815,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
@@ -4820,40 +4834,40 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-17 02:49</t>
+          <t>2026-10-17 02:41</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>84006</v>
+        <v>83998</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_No_2026</t>
+          <t>CFS_ARG_GK_ADK_E.MARTINEZ 23_2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>England World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4863,7 +4877,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-e-martinez-23-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
@@ -4882,40 +4896,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-17 02:57</t>
+          <t>2026-10-17 02:41</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>84015</v>
+        <v>83998</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CFS_CRC_HO_ADK_No_2026</t>
+          <t>CFS_ARG_GK_ADK_E.MARTINEZ 23_2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Curacao Away Adult Cheap Football Kit 2026/27</t>
+          <t>Argentina World Cup 2026 E.MARTINEZ 23 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Curacao Away Adult Cheap Football Kit 2026/27 , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4925,7 +4939,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/curacao-away-adult-cheap-football-kit-2026-27/</t>
+          <t>https://cheapfootballshirts.com/product/argentina-world-cup-2026-e-martinez-23-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
@@ -4944,40 +4958,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-17 02:57</t>
+          <t>2026-10-17 02:49</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>84015</v>
+        <v>84006</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CFS_CRC_HO_ADK_No_2026</t>
+          <t>CFS_ENG_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Curacao Away Adult Cheap Football Kit 2026/27</t>
+          <t>England World Cup 2026 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4987,7 +5001,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/curacao-away-adult-cheap-football-kit-2026-27/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
@@ -5006,40 +5020,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-17 03:06</t>
+          <t>2026-10-17 02:49</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>84023</v>
+        <v>84006</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CFS_CHE_BlackTN_ADK_No_2026</t>
+          <t>CFS_ENG_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Chelsea Black Training Adult Cheap Football Kit 2026/27</t>
+          <t>England World Cup 2026 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Chelsea Black Training Adult Cheap Football Kit 2026/27 , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5049,7 +5063,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/chelsea-black-training-adult-cheap-football-kit-2026-27/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
@@ -5068,40 +5082,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-17 03:06</t>
+          <t>2026-10-17 02:57</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>84023</v>
+        <v>84015</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CFS_CHE_BlackTN_ADK_No_2026</t>
+          <t>CFS_CRC_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Chelsea Black Training Adult Cheap Football Kit 2026/27</t>
+          <t>Curacao Away Adult Cheap Football Kit 2026/27</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Curacao Away Adult Cheap Football Kit 2026/27 , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5111,7 +5125,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/chelsea-black-training-adult-cheap-football-kit-2026-27/</t>
+          <t>https://cheapfootballshirts.com/product/curacao-away-adult-cheap-football-kit-2026-27/</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
@@ -5130,40 +5144,40 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-17 03:12</t>
+          <t>2026-10-17 02:57</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>84031</v>
+        <v>84015</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CFS_CHE_BlueTN_ADK_No_2026</t>
+          <t>CFS_CRC_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Chelsea Blue Training Adult Cheap Football Kit 2026/27</t>
+          <t>Curacao Away Adult Cheap Football Kit 2026/27</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Chelsea Blue Training Adult Cheap Football Kit 2026/27 , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5173,7 +5187,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/chelsea-blue-training-adult-cheap-football-kit-2026-27/</t>
+          <t>https://cheapfootballshirts.com/product/curacao-away-adult-cheap-football-kit-2026-27/</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
@@ -5192,40 +5206,40 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-17 03:12</t>
+          <t>2026-10-17 03:06</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>84031</v>
+        <v>84023</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CFS_CHE_BlueTN_ADK_No_2026</t>
+          <t>CFS_CHE_BlackTN_ADK_No_2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Chelsea Blue Training Adult Cheap Football Kit 2026/27</t>
+          <t>Chelsea Black Training Adult Cheap Football Kit 2026/27</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Chelsea Black Training Adult Cheap Football Kit 2026/27 , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5235,7 +5249,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/chelsea-blue-training-adult-cheap-football-kit-2026-27/</t>
+          <t>https://cheapfootballshirts.com/product/chelsea-black-training-adult-cheap-football-kit-2026-27/</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
@@ -5254,40 +5268,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-17 03:18</t>
+          <t>2026-10-17 03:06</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>84039</v>
+        <v>84023</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_No_2026</t>
+          <t>CFS_CHE_BlackTN_ADK_No_2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>England World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>Chelsea Black Training Adult Cheap Football Kit 2026/27</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5297,7 +5311,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/chelsea-black-training-adult-cheap-football-kit-2026-27/</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
@@ -5316,40 +5330,40 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-17 03:18</t>
+          <t>2026-10-17 03:12</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>84039</v>
+        <v>84031</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_No_2026</t>
+          <t>CFS_CHE_BlueTN_ADK_No_2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>England World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>Chelsea Blue Training Adult Cheap Football Kit 2026/27</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Chelsea Blue Training Adult Cheap Football Kit 2026/27 , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5359,7 +5373,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/chelsea-blue-training-adult-cheap-football-kit-2026-27/</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
@@ -5378,40 +5392,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-17 03:24</t>
+          <t>2026-10-17 03:12</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>84047</v>
+        <v>84031</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_BELLINGHAM 10_2026</t>
+          <t>CFS_CHE_BlueTN_ADK_No_2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>England World Cup 2026 BELLINGHAM 10 Away Adult Cheap Football Kit</t>
+          <t>Chelsea Blue Training Adult Cheap Football Kit 2026/27</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 BELLINGHAM 10 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5421,7 +5435,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/chelsea-blue-training-adult-cheap-football-kit-2026-27/</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
@@ -5440,40 +5454,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-17 03:24</t>
+          <t>2026-10-17 03:18</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>84047</v>
+        <v>84039</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_BELLINGHAM 10_2026</t>
+          <t>CFS_ENG_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>England World Cup 2026 BELLINGHAM 10 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5483,7 +5497,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
@@ -5502,40 +5516,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-17 03:31</t>
+          <t>2026-10-17 03:18</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>84055</v>
+        <v>84039</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_KANE 9_2026</t>
+          <t>CFS_ENG_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>England World Cup 2026 KANE 9 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 KANE 9 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5545,7 +5559,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
@@ -5564,40 +5578,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-17 03:31</t>
+          <t>2026-10-17 03:24</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>84055</v>
+        <v>84047</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_KANE 9_2026</t>
+          <t>CFS_ENG_AW_ADK_BELLINGHAM 10_2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>England World Cup 2026 KANE 9 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 BELLINGHAM 10 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 BELLINGHAM 10 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5607,7 +5621,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
@@ -5626,40 +5640,40 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-17 03:36</t>
+          <t>2026-10-17 03:24</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>84063</v>
+        <v>84047</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_RICE 4_2026</t>
+          <t>CFS_ENG_AW_ADK_BELLINGHAM 10_2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>England World Cup 2026 RICE 4 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 BELLINGHAM 10 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 RICE 4 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5669,7 +5683,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
@@ -5688,40 +5702,40 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-17 03:36</t>
+          <t>2026-10-17 03:31</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>84063</v>
+        <v>84055</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_RICE 4_2026</t>
+          <t>CFS_ENG_AW_ADK_KANE 9_2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>England World Cup 2026 RICE 4 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 KANE 9 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 KANE 9 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5731,7 +5745,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
@@ -5750,40 +5764,40 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-17 03:40</t>
+          <t>2026-10-17 03:31</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>84071</v>
+        <v>84055</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_SAKA 7_2026</t>
+          <t>CFS_ENG_AW_ADK_KANE 9_2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>England World Cup 2026 SAKA 7 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 KANE 9 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 SAKA 7 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5793,7 +5807,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
@@ -5812,40 +5826,40 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-17 03:40</t>
+          <t>2026-10-17 03:36</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>84071</v>
+        <v>84063</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CFS_ENG_AW_ADK_SAKA 7_2026</t>
+          <t>CFS_ENG_AW_ADK_RICE 4_2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>England World Cup 2026 SAKA 7 Away Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 RICE 4 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 RICE 4 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5855,7 +5869,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr">
@@ -5874,40 +5888,40 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-10-17 03:47</t>
+          <t>2026-10-17 03:36</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>84079</v>
+        <v>84063</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CFS_ENG_BlueGK_ADK_No_2026</t>
+          <t>CFS_ENG_AW_ADK_RICE 4_2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>England World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 RICE 4 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5917,7 +5931,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-blue-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
@@ -5936,40 +5950,40 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-17 03:47</t>
+          <t>2026-10-17 03:40</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>84079</v>
+        <v>84071</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CFS_ENG_BlueGK_ADK_No_2026</t>
+          <t>CFS_ENG_AW_ADK_SAKA 7_2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>England World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 SAKA 7 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 SAKA 7 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5979,7 +5993,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-blue-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr">
@@ -5998,40 +6012,40 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-17 03:58</t>
+          <t>2026-10-17 03:40</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>84089</v>
+        <v>84071</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CFS_ENG_YellowGK_ADK_No_2026</t>
+          <t>CFS_ENG_AW_ADK_SAKA 7_2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>England World Cup 2026 Yellow Goalkeeper Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 SAKA 7 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 Yellow Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6041,7 +6055,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-yellow-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr">
@@ -6060,20 +6074,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-17 04:06</t>
+          <t>2026-10-17 03:47</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>84098</v>
+        <v>84079</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_BELLINGHAM 10_2026</t>
+          <t>CFS_ENG_BlueGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>England World Cup 2026 BELLINGHAM 10 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6088,7 +6102,7 @@
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 BELLINGHAM 10 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
@@ -6103,7 +6117,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-blue-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr">
@@ -6122,40 +6136,40 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-10-17 04:12</t>
+          <t>2026-10-17 03:47</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>84107</v>
+        <v>84079</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_KANE 9_2026</t>
+          <t>CFS_ENG_BlueGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>England World Cup 2026 KANE 9 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 KANE 9 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6165,7 +6179,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-blue-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr">
@@ -6184,20 +6198,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-10-17 04:16</t>
+          <t>2026-10-17 03:58</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>84116</v>
+        <v>84089</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_RICE 4_2026</t>
+          <t>CFS_ENG_YellowGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>England World Cup 2026 RICE 4 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 Yellow Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6212,7 +6226,7 @@
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 RICE 4 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 Yellow Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
@@ -6227,7 +6241,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-yellow-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr">
@@ -6246,20 +6260,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-10-17 04:20</t>
+          <t>2026-10-17 04:06</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>84125</v>
+        <v>84098</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>CFS_ENG_HO_ADK_SAKA 7_2026</t>
+          <t>CFS_ENG_HO_ADK_BELLINGHAM 10_2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>England World Cup 2026 SAKA 7 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 BELLINGHAM 10 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6274,7 +6288,7 @@
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 SAKA 7 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 BELLINGHAM 10 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
@@ -6289,7 +6303,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-bellingham-10-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr">
@@ -6308,20 +6322,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-10-17 06:47</t>
+          <t>2026-10-17 04:12</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>84135</v>
+        <v>84107</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>CFS_GER_AWGK_ADK_No_2026</t>
+          <t>CFS_ENG_HO_ADK_KANE 9_2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Germany World Cup 2026 Away Goalkeeper Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 KANE 9 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6336,7 +6350,7 @@
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Germany World Cup 2026 Away Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 KANE 9 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
@@ -6351,7 +6365,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/germany-world-cup-2026-away-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-kane-9-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L94" s="6" t="inlineStr">
@@ -6370,40 +6384,40 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-10-17 06:47</t>
+          <t>2026-10-17 04:16</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>84135</v>
+        <v>84116</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>CFS_GER_AWGK_ADK_No_2026</t>
+          <t>CFS_ENG_HO_ADK_RICE 4_2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Germany World Cup 2026 Away Goalkeeper Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 RICE 4 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 RICE 4 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6413,7 +6427,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/germany-world-cup-2026-away-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-rice-4-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr">
@@ -6432,20 +6446,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-10-17 06:54</t>
+          <t>2026-10-17 04:20</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>84143</v>
+        <v>84125</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CFS_JP_HO_ADK_No_2026</t>
+          <t>CFS_ENG_HO_ADK_SAKA 7_2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Japan World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>England World Cup 2026 SAKA 7 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6460,7 +6474,7 @@
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Japan World Cup 2026 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>khoảng trắng trước dấu câu: "Get the England World Cup 2026 SAKA 7 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
@@ -6475,7 +6489,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/japan-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/england-world-cup-2026-saka-7-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr">
@@ -6494,20 +6508,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-10-17 06:59</t>
+          <t>2026-10-17 06:47</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>84151</v>
+        <v>84135</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CFS_NTL_BlackGK_ADK_No_2026</t>
+          <t>CFS_GER_AWGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Netherlands World Cup 2026 Black Goalkeeper Adult Cheap Football Kit</t>
+          <t>Germany World Cup 2026 Away Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6522,7 +6536,7 @@
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Netherlands World Cup 2026 Black Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>khoảng trắng trước dấu câu: "Get the Germany World Cup 2026 Away Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr">
@@ -6537,7 +6551,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-black-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/germany-world-cup-2026-away-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr">
@@ -6556,20 +6570,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-10-17 06:59</t>
+          <t>2026-10-17 06:47</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>84151</v>
+        <v>84135</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CFS_NTL_BlackGK_ADK_No_2026</t>
+          <t>CFS_GER_AWGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Netherlands World Cup 2026 Black Goalkeeper Adult Cheap Football Kit</t>
+          <t>Germany World Cup 2026 Away Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6599,7 +6613,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-black-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/germany-world-cup-2026-away-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L98" s="6" t="inlineStr">
@@ -6618,20 +6632,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-17 07:05</t>
+          <t>2026-10-17 06:54</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>84159</v>
+        <v>84143</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>CFS_NTL_GreenGK_ADK_No_2026</t>
+          <t>CFS_JP_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Netherlands World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
+          <t>Japan World Cup 2026 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6646,7 +6660,7 @@
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Netherlands World Cup 2026 Green Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>khoảng trắng trước dấu câu: "Get the Japan World Cup 2026 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr">
@@ -6661,7 +6675,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/japan-world-cup-2026-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
@@ -6680,40 +6694,40 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-10-17 07:05</t>
+          <t>2026-10-17 06:59</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>84159</v>
+        <v>84151</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CFS_NTL_GreenGK_ADK_No_2026</t>
+          <t>CFS_NTL_BlackGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Netherlands World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
+          <t>Netherlands World Cup 2026 Black Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Netherlands World Cup 2026 Black Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6723,7 +6737,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-black-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr">
@@ -6742,40 +6756,40 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-10-17 07:09</t>
+          <t>2026-10-17 06:59</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>84167</v>
+        <v>84151</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>CFS_SCL_AW_ADK_No_2026</t>
+          <t>CFS_NTL_BlackGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>Netherlands World Cup 2026 Black Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Scotland World Cup 2026 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6785,7 +6799,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-black-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
@@ -6804,40 +6818,40 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-17 07:09</t>
+          <t>2026-10-17 07:05</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>84167</v>
+        <v>84159</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>CFS_SCL_AW_ADK_No_2026</t>
+          <t>CFS_NTL_GreenGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>Netherlands World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Netherlands World Cup 2026 Green Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6847,7 +6861,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr">
@@ -6866,40 +6880,40 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-10-17 07:14</t>
+          <t>2026-10-17 07:05</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>84176</v>
+        <v>84159</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CFS_SCL_AW_ADK_McTOMINAY 4_2026</t>
+          <t>CFS_NTL_GreenGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 McTOMINAY 4 Away Adult Cheap Football Kit</t>
+          <t>Netherlands World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Scotland World Cup 2026 McTOMINAY 4 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6909,7 +6923,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/netherlands-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr">
@@ -6928,40 +6942,40 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-10-17 07:14</t>
+          <t>2026-10-17 07:09</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>84176</v>
+        <v>84167</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CFS_SCL_AW_ADK_McTOMINAY 4_2026</t>
+          <t>CFS_SCL_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 McTOMINAY 4 Away Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Scotland World Cup 2026 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6971,7 +6985,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L104" s="6" t="inlineStr">
@@ -6990,40 +7004,40 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-10-17 07:23</t>
+          <t>2026-10-17 07:09</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>84185</v>
+        <v>84167</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>CFS_SCL_HO_ADK_No_2026</t>
+          <t>CFS_SCL_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Scotland World Cup 2026 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7033,7 +7047,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr">
@@ -7052,40 +7066,40 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-10-17 07:23</t>
+          <t>2026-10-17 07:14</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>84185</v>
+        <v>84176</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>CFS_SCL_HO_ADK_No_2026</t>
+          <t>CFS_SCL_AW_ADK_McTOMINAY 4_2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 McTOMINAY 4 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Scotland World Cup 2026 McTOMINAY 4 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7095,7 +7109,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L106" s="6" t="inlineStr">
@@ -7114,40 +7128,40 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-10-17 07:27</t>
+          <t>2026-10-17 07:14</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>84193</v>
+        <v>84176</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>CFS_SCL_HO_ADK_McTOMINAY 4_2026</t>
+          <t>CFS_SCL_AW_ADK_McTOMINAY 4_2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 McTOMINAY 4 Home Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 McTOMINAY 4 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Scotland World Cup 2026 McTOMINAY 4 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7157,7 +7171,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr">
@@ -7176,20 +7190,20 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-10-17 07:32</t>
+          <t>2026-10-17 07:23</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>84203</v>
+        <v>84185</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CFS_SCL_HO_ADK_MCGINN 7_2026</t>
+          <t>CFS_SCL_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Scotland World Cup 2026 MCGINN 7 Home Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7204,7 +7218,7 @@
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Scotland World Cup 2026 MCGINN 7 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>khoảng trắng trước dấu câu: "Get the Scotland World Cup 2026 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
@@ -7219,7 +7233,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mcginn-7-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L108" s="6" t="inlineStr">
@@ -7238,40 +7252,40 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-10-17 07:36</t>
+          <t>2026-10-17 07:23</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>84212</v>
+        <v>84185</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CFS_SPA_BlueGK_ADK_No_2026</t>
+          <t>CFS_SCL_HO_ADK_No_2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Spain World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7281,7 +7295,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-blue-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr">
@@ -7300,20 +7314,20 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-10-17 07:41</t>
+          <t>2026-10-17 07:27</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>84219</v>
+        <v>84193</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>CFS_SPA_GK_ADK_No_2026</t>
+          <t>CFS_SCL_HO_ADK_McTOMINAY 4_2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 McTOMINAY 4 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7328,7 +7342,7 @@
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Spain World Cup 2026 Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>khoảng trắng trước dấu câu: "Get the Scotland World Cup 2026 McTOMINAY 4 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr">
@@ -7343,7 +7357,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mctominay-4-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L110" s="6" t="inlineStr">
@@ -7362,20 +7376,20 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-10-17 07:44</t>
+          <t>2026-10-17 07:32</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>84226</v>
+        <v>84203</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>CFS_SPA_GK_ADK_RAYA 1_2026</t>
+          <t>CFS_SCL_HO_ADK_MCGINN 7_2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 RAYA 1 Goalkeeper Adult Cheap Football Kit</t>
+          <t>Scotland World Cup 2026 MCGINN 7 Home Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7390,7 +7404,7 @@
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Spain World Cup 2026 RAYA 1 Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>khoảng trắng trước dấu câu: "Get the Scotland World Cup 2026 MCGINN 7 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr">
@@ -7405,7 +7419,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-raya-1-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/scotland-world-cup-2026-mcginn-7-home-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr">
@@ -7424,40 +7438,40 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-10-17 07:44</t>
+          <t>2026-10-17 07:36</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>84226</v>
+        <v>84212</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CFS_SPA_GK_ADK_RAYA 1_2026</t>
+          <t>CFS_SPA_BlueGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 RAYA 1 Goalkeeper Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Spain World Cup 2026 Blue Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7467,7 +7481,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-raya-1-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-blue-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L112" s="6" t="inlineStr">
@@ -7486,20 +7500,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-10-17 07:50</t>
+          <t>2026-10-17 07:41</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>84234</v>
+        <v>84219</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CFS_SPA_GreenGK_ADK_No_2026</t>
+          <t>CFS_SPA_GK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7514,7 +7528,7 @@
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Spain World Cup 2026 Green Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>khoảng trắng trước dấu câu: "Get the Spain World Cup 2026 Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr">
@@ -7529,7 +7543,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr">
@@ -7548,40 +7562,40 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-10-17 07:50</t>
+          <t>2026-10-17 07:44</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>84234</v>
+        <v>84226</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CFS_SPA_GreenGK_ADK_No_2026</t>
+          <t>CFS_SPA_GK_ADK_RAYA 1_2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 RAYA 1 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Spain World Cup 2026 RAYA 1 Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7591,7 +7605,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-raya-1-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L114" s="6" t="inlineStr">
@@ -7610,40 +7624,40 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-10-17 07:54</t>
+          <t>2026-10-17 07:44</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>84242</v>
+        <v>84226</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CFS_SPA_RedGK_ADK_No_2026</t>
+          <t>CFS_SPA_GK_ADK_RAYA 1_2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 Red Goalkeeper Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 RAYA 1 Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Spain World Cup 2026 Red Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7653,7 +7667,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-red-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-raya-1-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr">
@@ -7672,40 +7686,40 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-10-17 07:54</t>
+          <t>2026-10-17 07:50</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>84242</v>
+        <v>84234</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>CFS_SPA_RedGK_ADK_No_2026</t>
+          <t>CFS_SPA_GreenGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Spain World Cup 2026 Red Goalkeeper Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Spain World Cup 2026 Green Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7715,7 +7729,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-red-goalkeeper-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L116" s="6" t="inlineStr">
@@ -7734,40 +7748,40 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-10-17 07:58</t>
+          <t>2026-10-17 07:50</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>84250</v>
+        <v>84234</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>CFS_URU_AW_ADK_No_2026</t>
+          <t>CFS_SPA_GreenGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Uruguay World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 Green Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Uruguay World Cup 2026 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7777,7 +7791,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/uruguay-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-green-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr">
@@ -7796,40 +7810,40 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-10-17 07:58</t>
+          <t>2026-10-17 07:54</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>84250</v>
+        <v>84242</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CFS_URU_AW_ADK_No_2026</t>
+          <t>CFS_SPA_RedGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Uruguay World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 Red Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ảnh</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Số lượng ảnh</t>
+          <t>Meta description</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
+          <t>khoảng trắng trước dấu câu: "Get the Spain World Cup 2026 Red Goalkeeper Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Thêm ảnh</t>
+          <t>Sửa định dạng</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7839,7 +7853,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/uruguay-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-red-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr">
@@ -7858,40 +7872,40 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-10-17 08:05</t>
+          <t>2026-10-17 07:54</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>84258</v>
+        <v>84242</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>CFS_USA_AW_ADK_No_2026</t>
+          <t>CFS_SPA_RedGK_ADK_No_2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>USA World Cup 2026 Away Adult Cheap Football Kit</t>
+          <t>Spain World Cup 2026 Red Goalkeeper Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the USA World Cup 2026 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7901,7 +7915,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-away-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/spain-world-cup-2026-red-goalkeeper-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr">
@@ -7920,20 +7934,20 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-10-17 08:12</t>
+          <t>2026-10-17 07:58</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>84266</v>
+        <v>84250</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CFS_USA_HO_ADK_No_2026</t>
+          <t>CFS_URU_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>USA World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>Uruguay World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7948,7 +7962,7 @@
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the USA World Cup 2026 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>khoảng trắng trước dấu câu: "Get the Uruguay World Cup 2026 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
@@ -7963,7 +7977,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/uruguay-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr">
@@ -7982,40 +7996,40 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-10-17 08:18</t>
+          <t>2026-10-17 07:58</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>84273</v>
+        <v>84250</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>CFS_WAL_HO_ADK_No_2026</t>
+          <t>CFS_URU_AW_ADK_No_2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Wales World Cup 2026 Home Adult Cheap Football Kit</t>
+          <t>Uruguay World Cup 2026 Away Adult Cheap Football Kit</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Meta description</t>
+          <t>Số lượng ảnh</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>khoảng trắng trước dấu câu: "Get the Wales World Cup 2026 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+          <t>Chỉ có 2 ảnh sản phẩm (nên ≥ 3: trước / sau / chi tiết)</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Sửa định dạng</t>
+          <t>Thêm ảnh</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8025,7 +8039,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>https://cheapfootballshirts.com/product/wales-world-cup-2026-home-adult-cheap-football-kit/</t>
+          <t>https://cheapfootballshirts.com/product/uruguay-world-cup-2026-away-adult-cheap-football-kit/</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr">
@@ -8036,8 +8050,194 @@
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
     </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:05</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>84258</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>CFS_USA_AW_ADK_No_2026</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>USA World Cup 2026 Away Adult Cheap Football Kit</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Meta description</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>khoảng trắng trước dấu câu: "Get the USA World Cup 2026 Away Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>Sửa định dạng</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-away-adult-cheap-football-kit/</t>
+        </is>
+      </c>
+      <c r="L122" s="6" t="inlineStr">
+        <is>
+          <t>Mở</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:12</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>84266</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>CFS_USA_HO_ADK_No_2026</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>USA World Cup 2026 Home Adult Cheap Football Kit</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Meta description</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>khoảng trắng trước dấu câu: "Get the USA World Cup 2026 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>Sửa định dạng</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>https://cheapfootballshirts.com/product/usa-world-cup-2026-home-adult-cheap-football-kit/</t>
+        </is>
+      </c>
+      <c r="L123" s="6" t="inlineStr">
+        <is>
+          <t>Mở</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:18</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>84273</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CFS_WAL_HO_ADK_No_2026</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Wales World Cup 2026 Home Adult Cheap Football Kit</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Meta description</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>khoảng trắng trước dấu câu: "Get the Wales World Cup 2026 Home Adult Cheap Football Kit , High Quality, Discounted Price, Risk-Free Shopping, Quick Support. Order now at Cheap Football Shirts ⚽️"</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>Sửa định dạng</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>https://cheapfootballshirts.com/product/wales-world-cup-2026-home-adult-cheap-football-kit/</t>
+        </is>
+      </c>
+      <c r="L124" s="6" t="inlineStr">
+        <is>
+          <t>Mở</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N121"/>
+  <autoFilter ref="A1:N124"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -8279,6 +8479,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId239"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId246"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
